--- a/EquiposUnidos/app/src/main/res/raw/template_preven_excava.xlsx
+++ b/EquiposUnidos/app/src/main/res/raw/template_preven_excava.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Developer user\android\williApp\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212ED384-46D4-49A1-9079-027827A9C740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EAF05E-E611-4BCD-B522-BDF435675E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FT-MANT-10" sheetId="14" r:id="rId1"/>
@@ -1289,6 +1289,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1422,6 +1428,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1502,19 +1514,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2374,7 +2374,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B1" s="55"/>
+      <c r="B1" s="57"/>
       <c r="C1" s="30" t="s">
         <v>115</v>
       </c>
@@ -2391,7 +2391,7 @@
       </c>
     </row>
     <row r="2" spans="2:10" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B2" s="56"/>
+      <c r="B2" s="58"/>
       <c r="C2" s="33"/>
       <c r="D2" s="34"/>
       <c r="E2" s="34"/>
@@ -2406,7 +2406,7 @@
       </c>
     </row>
     <row r="3" spans="2:10" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B3" s="57"/>
+      <c r="B3" s="59"/>
       <c r="C3" s="36"/>
       <c r="D3" s="37"/>
       <c r="E3" s="37"/>
@@ -2421,30 +2421,30 @@
       </c>
     </row>
     <row r="4" spans="2:10" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B4" s="58"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="60"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="2:10" s="3" customFormat="1" ht="33" customHeight="1">
       <c r="B5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="112"/>
-      <c r="J5" s="68" t="s">
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="70" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2453,81 +2453,81 @@
         <v>6</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="68"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="70"/>
     </row>
     <row r="7" spans="2:10" s="3" customFormat="1" ht="33" customHeight="1">
       <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="45"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="47"/>
     </row>
     <row r="8" spans="2:10" s="3" customFormat="1" ht="33" customHeight="1">
       <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="111" t="s">
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="I8" s="112"/>
-      <c r="J8" s="46"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="48"/>
     </row>
     <row r="9" spans="2:10" s="3" customFormat="1" ht="42" customHeight="1">
       <c r="B9" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="111"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="47"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" spans="2:10" s="3" customFormat="1" ht="33" customHeight="1">
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="63"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="65"/>
     </row>
     <row r="11" spans="2:10" s="3" customFormat="1" ht="45" customHeight="1">
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="62"/>
+      <c r="C11" s="64"/>
       <c r="D11" s="20" t="s">
         <v>11</v>
       </c>
@@ -2543,38 +2543,38 @@
       <c r="H11" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="63" t="s">
+      <c r="I11" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="J11" s="63"/>
-    </row>
-    <row r="12" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B12" s="53" t="s">
+      <c r="J11" s="65"/>
+    </row>
+    <row r="12" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B12" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="73"/>
+      <c r="C12" s="75"/>
       <c r="D12" s="26"/>
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
       <c r="H12" s="27"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="72"/>
-    </row>
-    <row r="13" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B13" s="67" t="s">
+      <c r="I12" s="73"/>
+      <c r="J12" s="74"/>
+    </row>
+    <row r="13" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B13" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="67"/>
+      <c r="C13" s="69"/>
       <c r="D13" s="27"/>
       <c r="E13" s="27"/>
       <c r="F13" s="27"/>
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="49"/>
-    </row>
-    <row r="14" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="I13" s="50"/>
+      <c r="J13" s="51"/>
+    </row>
+    <row r="14" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B14" s="10" t="s">
         <v>25</v>
       </c>
@@ -2584,10 +2584,10 @@
       <c r="F14" s="27"/>
       <c r="G14" s="27"/>
       <c r="H14" s="27"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="49"/>
-    </row>
-    <row r="15" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="I14" s="54"/>
+      <c r="J14" s="51"/>
+    </row>
+    <row r="15" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B15" s="23" t="s">
         <v>18</v>
       </c>
@@ -2600,11 +2600,11 @@
       <c r="I15" s="24"/>
       <c r="J15" s="25"/>
     </row>
-    <row r="16" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B16" s="50" t="s">
+    <row r="16" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B16" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="51"/>
+      <c r="C16" s="53"/>
       <c r="D16" s="27"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27" t="s">
@@ -2612,231 +2612,231 @@
       </c>
       <c r="G16" s="14"/>
       <c r="H16" s="14"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="49"/>
-    </row>
-    <row r="17" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B17" s="50" t="s">
+      <c r="I16" s="54"/>
+      <c r="J16" s="51"/>
+    </row>
+    <row r="17" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B17" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="51"/>
+      <c r="C17" s="53"/>
       <c r="D17" s="27"/>
       <c r="E17" s="27"/>
       <c r="F17" s="27"/>
       <c r="G17" s="14"/>
       <c r="H17" s="14"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="49"/>
-    </row>
-    <row r="18" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B18" s="53" t="s">
+      <c r="I17" s="54"/>
+      <c r="J17" s="51"/>
+    </row>
+    <row r="18" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B18" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="54"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="27"/>
       <c r="E18" s="27"/>
       <c r="F18" s="27"/>
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="49"/>
-    </row>
-    <row r="19" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B19" s="53" t="s">
+      <c r="I18" s="54"/>
+      <c r="J18" s="51"/>
+    </row>
+    <row r="19" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B19" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="54"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="27"/>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="49"/>
-    </row>
-    <row r="20" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B20" s="53" t="s">
+      <c r="I19" s="54"/>
+      <c r="J19" s="51"/>
+    </row>
+    <row r="20" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B20" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="54"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="27"/>
       <c r="E20" s="27"/>
       <c r="F20" s="27"/>
       <c r="G20" s="14"/>
       <c r="H20" s="14"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="49"/>
-    </row>
-    <row r="21" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B21" s="53" t="s">
+      <c r="I20" s="54"/>
+      <c r="J20" s="51"/>
+    </row>
+    <row r="21" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B21" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="54"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="27"/>
       <c r="E21" s="27"/>
       <c r="F21" s="27"/>
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="49"/>
-    </row>
-    <row r="22" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B22" s="50" t="s">
+      <c r="I21" s="54"/>
+      <c r="J21" s="51"/>
+    </row>
+    <row r="22" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B22" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="51"/>
+      <c r="C22" s="53"/>
       <c r="D22" s="27"/>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="49"/>
-    </row>
-    <row r="23" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B23" s="53" t="s">
+      <c r="I22" s="54"/>
+      <c r="J22" s="51"/>
+    </row>
+    <row r="23" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B23" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="54"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="27"/>
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="49"/>
-    </row>
-    <row r="24" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B24" s="53" t="s">
+      <c r="I23" s="54"/>
+      <c r="J23" s="51"/>
+    </row>
+    <row r="24" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B24" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="54"/>
+      <c r="C24" s="56"/>
       <c r="D24" s="27"/>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="49"/>
-    </row>
-    <row r="25" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B25" s="53" t="s">
+      <c r="I24" s="54"/>
+      <c r="J24" s="51"/>
+    </row>
+    <row r="25" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B25" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="54"/>
+      <c r="C25" s="56"/>
       <c r="D25" s="27"/>
       <c r="E25" s="27"/>
       <c r="F25" s="27"/>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="49"/>
-    </row>
-    <row r="26" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B26" s="50" t="s">
+      <c r="I25" s="54"/>
+      <c r="J25" s="51"/>
+    </row>
+    <row r="26" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B26" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="51"/>
+      <c r="C26" s="53"/>
       <c r="D26" s="27"/>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="49"/>
-    </row>
-    <row r="27" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B27" s="53" t="s">
+      <c r="I26" s="54"/>
+      <c r="J26" s="51"/>
+    </row>
+    <row r="27" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B27" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="54"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="27"/>
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="49"/>
-    </row>
-    <row r="28" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B28" s="53" t="s">
+      <c r="I27" s="54"/>
+      <c r="J27" s="51"/>
+    </row>
+    <row r="28" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B28" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="54"/>
+      <c r="C28" s="56"/>
       <c r="D28" s="27"/>
       <c r="E28" s="27"/>
       <c r="F28" s="27"/>
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="49"/>
-    </row>
-    <row r="29" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B29" s="81" t="s">
+      <c r="I28" s="54"/>
+      <c r="J28" s="51"/>
+    </row>
+    <row r="29" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B29" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="82"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="82"/>
-      <c r="F29" s="82"/>
-      <c r="G29" s="82"/>
-      <c r="H29" s="82"/>
-      <c r="I29" s="82"/>
-      <c r="J29" s="83"/>
-    </row>
-    <row r="30" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B30" s="50" t="s">
+      <c r="C29" s="86"/>
+      <c r="D29" s="86"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="86"/>
+      <c r="G29" s="86"/>
+      <c r="H29" s="86"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="87"/>
+    </row>
+    <row r="30" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B30" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="C30" s="51"/>
+      <c r="C30" s="53"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="49"/>
-    </row>
-    <row r="31" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B31" s="53" t="s">
+      <c r="I30" s="54"/>
+      <c r="J30" s="51"/>
+    </row>
+    <row r="31" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B31" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="54"/>
+      <c r="C31" s="56"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="49"/>
-    </row>
-    <row r="32" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B32" s="53" t="s">
+      <c r="I31" s="54"/>
+      <c r="J31" s="51"/>
+    </row>
+    <row r="32" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B32" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="54"/>
+      <c r="C32" s="56"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="28"/>
       <c r="H32" s="28"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="49"/>
-    </row>
-    <row r="33" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B33" s="50" t="s">
+      <c r="I32" s="54"/>
+      <c r="J32" s="51"/>
+    </row>
+    <row r="33" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B33" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="C33" s="51"/>
+      <c r="C33" s="53"/>
       <c r="D33" s="27"/>
       <c r="E33" s="27"/>
       <c r="F33" s="27"/>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="49"/>
-    </row>
-    <row r="34" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="I33" s="54"/>
+      <c r="J33" s="51"/>
+    </row>
+    <row r="34" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B34" s="23" t="s">
         <v>24</v>
       </c>
@@ -2849,46 +2849,46 @@
       <c r="I34" s="24"/>
       <c r="J34" s="25"/>
     </row>
-    <row r="35" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B35" s="65" t="s">
+    <row r="35" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B35" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="66"/>
+      <c r="C35" s="68"/>
       <c r="D35" s="27"/>
       <c r="E35" s="27"/>
       <c r="F35" s="27"/>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="49"/>
-    </row>
-    <row r="36" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B36" s="65" t="s">
+      <c r="I35" s="54"/>
+      <c r="J35" s="51"/>
+    </row>
+    <row r="36" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B36" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="66"/>
+      <c r="C36" s="68"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
       <c r="F36" s="27"/>
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="49"/>
-    </row>
-    <row r="37" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B37" s="50" t="s">
+      <c r="I36" s="54"/>
+      <c r="J36" s="51"/>
+    </row>
+    <row r="37" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B37" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="51"/>
+      <c r="C37" s="53"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
       <c r="F37" s="27"/>
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="49"/>
-    </row>
-    <row r="38" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="I37" s="54"/>
+      <c r="J37" s="51"/>
+    </row>
+    <row r="38" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B38" s="23" t="s">
         <v>13</v>
       </c>
@@ -2901,150 +2901,150 @@
       <c r="I38" s="24"/>
       <c r="J38" s="25"/>
     </row>
-    <row r="39" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B39" s="50" t="s">
+    <row r="39" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B39" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="C39" s="51"/>
+      <c r="C39" s="53"/>
       <c r="D39" s="27"/>
       <c r="E39" s="27"/>
       <c r="F39" s="27"/>
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
-      <c r="I39" s="52"/>
-      <c r="J39" s="49"/>
-    </row>
-    <row r="40" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B40" s="53" t="s">
+      <c r="I39" s="54"/>
+      <c r="J39" s="51"/>
+    </row>
+    <row r="40" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B40" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C40" s="54"/>
+      <c r="C40" s="56"/>
       <c r="D40" s="27"/>
       <c r="E40" s="27"/>
       <c r="F40" s="27"/>
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="49"/>
-    </row>
-    <row r="41" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B41" s="50" t="s">
+      <c r="I40" s="54"/>
+      <c r="J40" s="51"/>
+    </row>
+    <row r="41" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B41" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="51"/>
+      <c r="C41" s="53"/>
       <c r="D41" s="27"/>
       <c r="E41" s="27"/>
       <c r="F41" s="27"/>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="49"/>
-    </row>
-    <row r="42" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B42" s="50" t="s">
+      <c r="I41" s="54"/>
+      <c r="J41" s="51"/>
+    </row>
+    <row r="42" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B42" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="51"/>
+      <c r="C42" s="53"/>
       <c r="D42" s="27"/>
       <c r="E42" s="27"/>
       <c r="F42" s="27"/>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="49"/>
-    </row>
-    <row r="43" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B43" s="53" t="s">
+      <c r="I42" s="54"/>
+      <c r="J42" s="51"/>
+    </row>
+    <row r="43" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B43" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="54"/>
+      <c r="C43" s="56"/>
       <c r="D43" s="27"/>
       <c r="E43" s="27"/>
       <c r="F43" s="27"/>
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="49"/>
-    </row>
-    <row r="44" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B44" s="53" t="s">
+      <c r="I43" s="54"/>
+      <c r="J43" s="51"/>
+    </row>
+    <row r="44" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B44" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="54"/>
+      <c r="C44" s="56"/>
       <c r="D44" s="27"/>
       <c r="E44" s="27"/>
       <c r="F44" s="27"/>
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="49"/>
-    </row>
-    <row r="45" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B45" s="69" t="s">
+      <c r="I44" s="54"/>
+      <c r="J44" s="51"/>
+    </row>
+    <row r="45" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B45" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="70"/>
+      <c r="C45" s="72"/>
       <c r="D45" s="27"/>
       <c r="E45" s="27"/>
       <c r="F45" s="27"/>
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="49"/>
-    </row>
-    <row r="46" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B46" s="67" t="s">
+      <c r="I45" s="54"/>
+      <c r="J45" s="51"/>
+    </row>
+    <row r="46" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B46" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="67"/>
+      <c r="C46" s="69"/>
       <c r="D46" s="27"/>
       <c r="E46" s="27"/>
       <c r="F46" s="27"/>
       <c r="G46" s="14"/>
       <c r="H46" s="14"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="49"/>
-    </row>
-    <row r="47" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B47" s="53" t="s">
+      <c r="I46" s="54"/>
+      <c r="J46" s="51"/>
+    </row>
+    <row r="47" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B47" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="C47" s="54"/>
+      <c r="C47" s="56"/>
       <c r="D47" s="27"/>
       <c r="E47" s="27"/>
       <c r="F47" s="27"/>
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
-      <c r="I47" s="52"/>
-      <c r="J47" s="49"/>
-    </row>
-    <row r="48" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B48" s="50" t="s">
+      <c r="I47" s="54"/>
+      <c r="J47" s="51"/>
+    </row>
+    <row r="48" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B48" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="C48" s="51"/>
+      <c r="C48" s="53"/>
       <c r="D48" s="27"/>
       <c r="E48" s="27"/>
       <c r="F48" s="27"/>
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
-      <c r="I48" s="52"/>
-      <c r="J48" s="49"/>
-    </row>
-    <row r="49" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B49" s="50" t="s">
+      <c r="I48" s="54"/>
+      <c r="J48" s="51"/>
+    </row>
+    <row r="49" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B49" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="51"/>
+      <c r="C49" s="53"/>
       <c r="D49" s="27"/>
       <c r="E49" s="27"/>
       <c r="F49" s="27"/>
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
-      <c r="I49" s="52"/>
-      <c r="J49" s="49"/>
-    </row>
-    <row r="50" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="I49" s="54"/>
+      <c r="J49" s="51"/>
+    </row>
+    <row r="50" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B50" s="23" t="s">
         <v>113</v>
       </c>
@@ -3057,85 +3057,85 @@
       <c r="I50" s="24"/>
       <c r="J50" s="25"/>
     </row>
-    <row r="51" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B51" s="53" t="s">
+    <row r="51" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B51" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="54"/>
+      <c r="C51" s="56"/>
       <c r="D51" s="27"/>
       <c r="E51" s="27"/>
       <c r="F51" s="27"/>
       <c r="G51" s="27"/>
       <c r="H51" s="27"/>
-      <c r="I51" s="108"/>
-      <c r="J51" s="109"/>
-    </row>
-    <row r="52" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B52" s="53" t="s">
+      <c r="I51" s="83"/>
+      <c r="J51" s="84"/>
+    </row>
+    <row r="52" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B52" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="54"/>
+      <c r="C52" s="56"/>
       <c r="D52" s="27"/>
       <c r="E52" s="27"/>
       <c r="F52" s="27"/>
       <c r="G52" s="27"/>
       <c r="H52" s="27"/>
-      <c r="I52" s="108"/>
-      <c r="J52" s="109"/>
-    </row>
-    <row r="53" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B53" s="53" t="s">
+      <c r="I52" s="83"/>
+      <c r="J52" s="84"/>
+    </row>
+    <row r="53" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B53" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="54"/>
+      <c r="C53" s="56"/>
       <c r="D53" s="27"/>
       <c r="E53" s="27"/>
       <c r="F53" s="27"/>
       <c r="G53" s="27"/>
       <c r="H53" s="27"/>
-      <c r="I53" s="108"/>
-      <c r="J53" s="109"/>
-    </row>
-    <row r="54" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B54" s="53" t="s">
+      <c r="I53" s="83"/>
+      <c r="J53" s="84"/>
+    </row>
+    <row r="54" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B54" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="54"/>
+      <c r="C54" s="56"/>
       <c r="D54" s="27"/>
       <c r="E54" s="27"/>
       <c r="F54" s="27"/>
       <c r="G54" s="27"/>
       <c r="H54" s="27"/>
-      <c r="I54" s="108"/>
-      <c r="J54" s="109"/>
-    </row>
-    <row r="55" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B55" s="53" t="s">
+      <c r="I54" s="83"/>
+      <c r="J54" s="84"/>
+    </row>
+    <row r="55" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B55" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="54"/>
+      <c r="C55" s="56"/>
       <c r="D55" s="27"/>
       <c r="E55" s="27"/>
       <c r="F55" s="27"/>
       <c r="G55" s="27"/>
       <c r="H55" s="27"/>
-      <c r="I55" s="108"/>
-      <c r="J55" s="109"/>
-    </row>
-    <row r="56" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B56" s="50" t="s">
+      <c r="I55" s="83"/>
+      <c r="J55" s="84"/>
+    </row>
+    <row r="56" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B56" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="C56" s="51"/>
+      <c r="C56" s="53"/>
       <c r="D56" s="27"/>
       <c r="E56" s="27"/>
       <c r="F56" s="27"/>
       <c r="G56" s="27"/>
       <c r="H56" s="27"/>
-      <c r="I56" s="48"/>
-      <c r="J56" s="49"/>
-    </row>
-    <row r="57" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="I56" s="50"/>
+      <c r="J56" s="51"/>
+    </row>
+    <row r="57" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B57" s="23" t="s">
         <v>16</v>
       </c>
@@ -3148,98 +3148,98 @@
       <c r="I57" s="24"/>
       <c r="J57" s="25"/>
     </row>
-    <row r="58" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B58" s="53" t="s">
+    <row r="58" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B58" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="54"/>
+      <c r="C58" s="56"/>
       <c r="D58" s="27"/>
       <c r="E58" s="27"/>
       <c r="F58" s="27"/>
       <c r="G58" s="27"/>
       <c r="H58" s="27"/>
-      <c r="I58" s="48"/>
-      <c r="J58" s="49"/>
-    </row>
-    <row r="59" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B59" s="53" t="s">
+      <c r="I58" s="50"/>
+      <c r="J58" s="51"/>
+    </row>
+    <row r="59" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B59" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="54"/>
+      <c r="C59" s="56"/>
       <c r="D59" s="27"/>
       <c r="E59" s="27"/>
       <c r="F59" s="27"/>
       <c r="G59" s="27"/>
       <c r="H59" s="27"/>
-      <c r="I59" s="52"/>
-      <c r="J59" s="49"/>
-    </row>
-    <row r="60" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B60" s="50" t="s">
+      <c r="I59" s="54"/>
+      <c r="J59" s="51"/>
+    </row>
+    <row r="60" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B60" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="C60" s="51"/>
+      <c r="C60" s="53"/>
       <c r="D60" s="27"/>
       <c r="E60" s="27"/>
       <c r="F60" s="27"/>
       <c r="G60" s="27"/>
       <c r="H60" s="27"/>
-      <c r="I60" s="52"/>
-      <c r="J60" s="49"/>
-    </row>
-    <row r="61" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B61" s="50" t="s">
+      <c r="I60" s="54"/>
+      <c r="J60" s="51"/>
+    </row>
+    <row r="61" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B61" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="C61" s="51"/>
+      <c r="C61" s="53"/>
       <c r="D61" s="27"/>
       <c r="E61" s="27"/>
       <c r="F61" s="27"/>
       <c r="G61" s="27"/>
       <c r="H61" s="27"/>
-      <c r="I61" s="52"/>
-      <c r="J61" s="49"/>
-    </row>
-    <row r="62" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B62" s="50" t="s">
+      <c r="I61" s="54"/>
+      <c r="J61" s="51"/>
+    </row>
+    <row r="62" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B62" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="C62" s="51"/>
+      <c r="C62" s="53"/>
       <c r="D62" s="27"/>
       <c r="E62" s="27"/>
       <c r="F62" s="27"/>
       <c r="G62" s="27"/>
       <c r="H62" s="27"/>
-      <c r="I62" s="52"/>
-      <c r="J62" s="49"/>
-    </row>
-    <row r="63" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B63" s="53" t="s">
+      <c r="I62" s="54"/>
+      <c r="J62" s="51"/>
+    </row>
+    <row r="63" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B63" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="C63" s="54"/>
+      <c r="C63" s="56"/>
       <c r="D63" s="27"/>
       <c r="E63" s="27"/>
       <c r="F63" s="27"/>
       <c r="G63" s="27"/>
       <c r="H63" s="27"/>
-      <c r="I63" s="52"/>
-      <c r="J63" s="49"/>
-    </row>
-    <row r="64" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B64" s="50" t="s">
+      <c r="I63" s="54"/>
+      <c r="J63" s="51"/>
+    </row>
+    <row r="64" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B64" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="C64" s="51"/>
+      <c r="C64" s="53"/>
       <c r="D64" s="27"/>
       <c r="E64" s="27"/>
       <c r="F64" s="27"/>
       <c r="G64" s="27"/>
       <c r="H64" s="27"/>
-      <c r="I64" s="48"/>
-      <c r="J64" s="49"/>
-    </row>
-    <row r="65" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="I64" s="50"/>
+      <c r="J64" s="51"/>
+    </row>
+    <row r="65" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B65" s="23" t="s">
         <v>73</v>
       </c>
@@ -3252,59 +3252,59 @@
       <c r="I65" s="24"/>
       <c r="J65" s="25"/>
     </row>
-    <row r="66" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B66" s="50" t="s">
+    <row r="66" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B66" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="C66" s="51"/>
+      <c r="C66" s="53"/>
       <c r="D66" s="27"/>
       <c r="E66" s="27"/>
       <c r="F66" s="27"/>
       <c r="G66" s="27"/>
       <c r="H66" s="27"/>
-      <c r="I66" s="48"/>
-      <c r="J66" s="49"/>
-    </row>
-    <row r="67" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B67" s="53" t="s">
+      <c r="I66" s="50"/>
+      <c r="J66" s="51"/>
+    </row>
+    <row r="67" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B67" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="C67" s="54"/>
+      <c r="C67" s="56"/>
       <c r="D67" s="27"/>
       <c r="E67" s="27"/>
       <c r="F67" s="27"/>
       <c r="G67" s="27"/>
       <c r="H67" s="27"/>
-      <c r="I67" s="52"/>
-      <c r="J67" s="49"/>
-    </row>
-    <row r="68" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B68" s="65" t="s">
+      <c r="I67" s="54"/>
+      <c r="J67" s="51"/>
+    </row>
+    <row r="68" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B68" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="66"/>
+      <c r="C68" s="68"/>
       <c r="D68" s="27"/>
       <c r="E68" s="27"/>
       <c r="F68" s="27"/>
       <c r="G68" s="27"/>
       <c r="H68" s="27"/>
-      <c r="I68" s="52"/>
-      <c r="J68" s="49"/>
-    </row>
-    <row r="69" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B69" s="50" t="s">
+      <c r="I68" s="54"/>
+      <c r="J68" s="51"/>
+    </row>
+    <row r="69" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B69" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="C69" s="51"/>
+      <c r="C69" s="53"/>
       <c r="D69" s="27"/>
       <c r="E69" s="27"/>
       <c r="F69" s="27"/>
       <c r="G69" s="27"/>
       <c r="H69" s="27"/>
-      <c r="I69" s="52"/>
-      <c r="J69" s="49"/>
-    </row>
-    <row r="70" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="I69" s="54"/>
+      <c r="J69" s="51"/>
+    </row>
+    <row r="70" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B70" s="23" t="s">
         <v>72</v>
       </c>
@@ -3317,33 +3317,33 @@
       <c r="I70" s="24"/>
       <c r="J70" s="25"/>
     </row>
-    <row r="71" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B71" s="53" t="s">
+    <row r="71" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B71" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C71" s="54"/>
+      <c r="C71" s="56"/>
       <c r="D71" s="27"/>
       <c r="E71" s="27"/>
       <c r="F71" s="27"/>
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
-      <c r="I71" s="52"/>
-      <c r="J71" s="49"/>
-    </row>
-    <row r="72" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B72" s="65" t="s">
+      <c r="I71" s="54"/>
+      <c r="J71" s="51"/>
+    </row>
+    <row r="72" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B72" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="C72" s="66"/>
+      <c r="C72" s="68"/>
       <c r="D72" s="27"/>
       <c r="E72" s="27"/>
       <c r="F72" s="27"/>
       <c r="G72" s="27"/>
       <c r="H72" s="27"/>
-      <c r="I72" s="52"/>
-      <c r="J72" s="49"/>
-    </row>
-    <row r="73" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="I72" s="54"/>
+      <c r="J72" s="51"/>
+    </row>
+    <row r="73" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B73" s="10" t="s">
         <v>71</v>
       </c>
@@ -3353,36 +3353,36 @@
       <c r="F73" s="27"/>
       <c r="G73" s="27"/>
       <c r="H73" s="27"/>
-      <c r="I73" s="52"/>
-      <c r="J73" s="49"/>
-    </row>
-    <row r="74" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B74" s="65" t="s">
+      <c r="I73" s="54"/>
+      <c r="J73" s="51"/>
+    </row>
+    <row r="74" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B74" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="C74" s="66"/>
+      <c r="C74" s="68"/>
       <c r="D74" s="27"/>
       <c r="E74" s="27"/>
       <c r="F74" s="27"/>
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
-      <c r="I74" s="52"/>
-      <c r="J74" s="49"/>
-    </row>
-    <row r="75" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B75" s="67" t="s">
+      <c r="I74" s="54"/>
+      <c r="J74" s="51"/>
+    </row>
+    <row r="75" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B75" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="C75" s="67"/>
+      <c r="C75" s="69"/>
       <c r="D75" s="27"/>
       <c r="E75" s="27"/>
       <c r="F75" s="27"/>
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
-      <c r="I75" s="110"/>
-      <c r="J75" s="110"/>
-    </row>
-    <row r="76" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="I75" s="112"/>
+      <c r="J75" s="112"/>
+    </row>
+    <row r="76" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B76" s="23" t="s">
         <v>17</v>
       </c>
@@ -3395,111 +3395,111 @@
       <c r="I76" s="24"/>
       <c r="J76" s="25"/>
     </row>
-    <row r="77" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B77" s="53" t="s">
+    <row r="77" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B77" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="C77" s="54"/>
+      <c r="C77" s="56"/>
       <c r="D77" s="27"/>
       <c r="E77" s="27"/>
       <c r="F77" s="27"/>
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
-      <c r="I77" s="52"/>
-      <c r="J77" s="49"/>
-    </row>
-    <row r="78" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B78" s="79" t="s">
+      <c r="I77" s="54"/>
+      <c r="J77" s="51"/>
+    </row>
+    <row r="78" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B78" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="C78" s="80"/>
+      <c r="C78" s="82"/>
       <c r="D78" s="27"/>
       <c r="E78" s="27"/>
       <c r="F78" s="27"/>
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
-      <c r="I78" s="52"/>
-      <c r="J78" s="49"/>
-    </row>
-    <row r="79" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B79" s="53" t="s">
+      <c r="I78" s="54"/>
+      <c r="J78" s="51"/>
+    </row>
+    <row r="79" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B79" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="C79" s="54"/>
+      <c r="C79" s="56"/>
       <c r="D79" s="27"/>
       <c r="E79" s="27"/>
       <c r="F79" s="27"/>
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
-      <c r="I79" s="52"/>
-      <c r="J79" s="49"/>
-    </row>
-    <row r="80" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B80" s="79" t="s">
+      <c r="I79" s="54"/>
+      <c r="J79" s="51"/>
+    </row>
+    <row r="80" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B80" s="81" t="s">
         <v>96</v>
       </c>
-      <c r="C80" s="80"/>
+      <c r="C80" s="82"/>
       <c r="D80" s="27"/>
       <c r="E80" s="27"/>
       <c r="F80" s="27"/>
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
-      <c r="I80" s="52"/>
-      <c r="J80" s="49"/>
-    </row>
-    <row r="81" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B81" s="79" t="s">
+      <c r="I80" s="54"/>
+      <c r="J80" s="51"/>
+    </row>
+    <row r="81" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B81" s="81" t="s">
         <v>78</v>
       </c>
-      <c r="C81" s="80"/>
+      <c r="C81" s="82"/>
       <c r="D81" s="27"/>
       <c r="E81" s="27"/>
       <c r="F81" s="27"/>
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
-      <c r="I81" s="52"/>
-      <c r="J81" s="49"/>
-    </row>
-    <row r="82" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B82" s="53" t="s">
+      <c r="I81" s="54"/>
+      <c r="J81" s="51"/>
+    </row>
+    <row r="82" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B82" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="C82" s="54"/>
+      <c r="C82" s="56"/>
       <c r="D82" s="27"/>
       <c r="E82" s="27"/>
       <c r="F82" s="27"/>
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
-      <c r="I82" s="52"/>
-      <c r="J82" s="49"/>
-    </row>
-    <row r="83" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B83" s="77" t="s">
+      <c r="I82" s="54"/>
+      <c r="J82" s="51"/>
+    </row>
+    <row r="83" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B83" s="79" t="s">
         <v>97</v>
       </c>
-      <c r="C83" s="78"/>
+      <c r="C83" s="80"/>
       <c r="D83" s="27"/>
       <c r="E83" s="27"/>
       <c r="F83" s="27"/>
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
-      <c r="I83" s="52"/>
-      <c r="J83" s="49"/>
-    </row>
-    <row r="84" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="B84" s="53" t="s">
+      <c r="I83" s="54"/>
+      <c r="J83" s="51"/>
+    </row>
+    <row r="84" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B84" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="C84" s="54"/>
+      <c r="C84" s="56"/>
       <c r="D84" s="27"/>
       <c r="E84" s="27"/>
       <c r="F84" s="27"/>
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
-      <c r="I84" s="52"/>
-      <c r="J84" s="49"/>
-    </row>
-    <row r="85" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="I84" s="54"/>
+      <c r="J84" s="51"/>
+    </row>
+    <row r="85" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B85" s="10" t="s">
         <v>75</v>
       </c>
@@ -3509,10 +3509,10 @@
       <c r="F85" s="27"/>
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
-      <c r="I85" s="52"/>
-      <c r="J85" s="49"/>
-    </row>
-    <row r="86" spans="2:10" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="I85" s="54"/>
+      <c r="J85" s="51"/>
+    </row>
+    <row r="86" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B86" s="10"/>
       <c r="C86" s="11"/>
       <c r="D86" s="16"/>
@@ -3523,307 +3523,307 @@
       <c r="I86" s="12"/>
       <c r="J86" s="13"/>
     </row>
-    <row r="87" spans="2:10" ht="30" customHeight="1">
-      <c r="B87" s="63" t="s">
+    <row r="87" spans="2:10" ht="21" customHeight="1">
+      <c r="B87" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="C87" s="63"/>
-      <c r="D87" s="64"/>
-      <c r="E87" s="64"/>
-      <c r="F87" s="64"/>
-      <c r="G87" s="64"/>
-      <c r="H87" s="64"/>
-      <c r="I87" s="64"/>
-      <c r="J87" s="63"/>
-    </row>
-    <row r="88" spans="2:10" ht="30" customHeight="1">
+      <c r="C87" s="65"/>
+      <c r="D87" s="66"/>
+      <c r="E87" s="66"/>
+      <c r="F87" s="66"/>
+      <c r="G87" s="66"/>
+      <c r="H87" s="66"/>
+      <c r="I87" s="66"/>
+      <c r="J87" s="65"/>
+    </row>
+    <row r="88" spans="2:10" ht="21" customHeight="1">
       <c r="B88" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="C88" s="52"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="74" t="s">
+      <c r="C88" s="54"/>
+      <c r="D88" s="50"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G88" s="75"/>
-      <c r="H88" s="76"/>
-      <c r="I88" s="52"/>
-      <c r="J88" s="49"/>
-    </row>
-    <row r="89" spans="2:10" ht="30" customHeight="1">
+      <c r="G88" s="77"/>
+      <c r="H88" s="78"/>
+      <c r="I88" s="54"/>
+      <c r="J88" s="51"/>
+    </row>
+    <row r="89" spans="2:10" ht="21" customHeight="1">
       <c r="B89" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="C89" s="52"/>
-      <c r="D89" s="48"/>
-      <c r="E89" s="49"/>
-      <c r="F89" s="74" t="s">
+      <c r="C89" s="54"/>
+      <c r="D89" s="50"/>
+      <c r="E89" s="51"/>
+      <c r="F89" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G89" s="75"/>
-      <c r="H89" s="76"/>
+      <c r="G89" s="77"/>
+      <c r="H89" s="78"/>
       <c r="I89" s="14"/>
       <c r="J89" s="13"/>
     </row>
-    <row r="90" spans="2:10" ht="30" customHeight="1">
+    <row r="90" spans="2:10" ht="21" customHeight="1">
       <c r="B90" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="C90" s="52"/>
-      <c r="D90" s="48"/>
-      <c r="E90" s="49"/>
-      <c r="F90" s="74" t="s">
+      <c r="C90" s="54"/>
+      <c r="D90" s="50"/>
+      <c r="E90" s="51"/>
+      <c r="F90" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G90" s="75"/>
-      <c r="H90" s="76"/>
-      <c r="I90" s="52"/>
-      <c r="J90" s="49"/>
-    </row>
-    <row r="91" spans="2:10" ht="30" customHeight="1">
+      <c r="G90" s="77"/>
+      <c r="H90" s="78"/>
+      <c r="I90" s="54"/>
+      <c r="J90" s="51"/>
+    </row>
+    <row r="91" spans="2:10" ht="21" customHeight="1">
       <c r="B91" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="C91" s="52"/>
-      <c r="D91" s="48"/>
-      <c r="E91" s="49"/>
-      <c r="F91" s="74" t="s">
+      <c r="C91" s="54"/>
+      <c r="D91" s="50"/>
+      <c r="E91" s="51"/>
+      <c r="F91" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G91" s="75"/>
-      <c r="H91" s="76"/>
-      <c r="I91" s="52"/>
-      <c r="J91" s="49"/>
-    </row>
-    <row r="92" spans="2:10" ht="30" customHeight="1">
+      <c r="G91" s="77"/>
+      <c r="H91" s="78"/>
+      <c r="I91" s="54"/>
+      <c r="J91" s="51"/>
+    </row>
+    <row r="92" spans="2:10" ht="21" customHeight="1">
       <c r="B92" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="C92" s="52"/>
-      <c r="D92" s="48"/>
-      <c r="E92" s="49"/>
-      <c r="F92" s="74" t="s">
+      <c r="C92" s="54"/>
+      <c r="D92" s="50"/>
+      <c r="E92" s="51"/>
+      <c r="F92" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G92" s="75"/>
-      <c r="H92" s="76"/>
-      <c r="I92" s="52"/>
-      <c r="J92" s="49"/>
-    </row>
-    <row r="93" spans="2:10" ht="30" customHeight="1">
+      <c r="G92" s="77"/>
+      <c r="H92" s="78"/>
+      <c r="I92" s="54"/>
+      <c r="J92" s="51"/>
+    </row>
+    <row r="93" spans="2:10" ht="21" customHeight="1">
       <c r="B93" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="C93" s="52"/>
-      <c r="D93" s="48"/>
-      <c r="E93" s="49"/>
-      <c r="F93" s="74" t="s">
+      <c r="C93" s="54"/>
+      <c r="D93" s="50"/>
+      <c r="E93" s="51"/>
+      <c r="F93" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G93" s="75"/>
-      <c r="H93" s="76"/>
-      <c r="I93" s="52"/>
-      <c r="J93" s="49"/>
-    </row>
-    <row r="94" spans="2:10" ht="30" customHeight="1">
+      <c r="G93" s="77"/>
+      <c r="H93" s="78"/>
+      <c r="I93" s="54"/>
+      <c r="J93" s="51"/>
+    </row>
+    <row r="94" spans="2:10" ht="21" customHeight="1">
       <c r="B94" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C94" s="52"/>
-      <c r="D94" s="48"/>
-      <c r="E94" s="49"/>
-      <c r="F94" s="74" t="s">
+      <c r="C94" s="54"/>
+      <c r="D94" s="50"/>
+      <c r="E94" s="51"/>
+      <c r="F94" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G94" s="75"/>
-      <c r="H94" s="76"/>
-      <c r="I94" s="52"/>
-      <c r="J94" s="49"/>
-    </row>
-    <row r="95" spans="2:10" ht="30" customHeight="1">
+      <c r="G94" s="77"/>
+      <c r="H94" s="78"/>
+      <c r="I94" s="54"/>
+      <c r="J94" s="51"/>
+    </row>
+    <row r="95" spans="2:10" ht="21" customHeight="1">
       <c r="B95" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="C95" s="52"/>
-      <c r="D95" s="48"/>
-      <c r="E95" s="49"/>
-      <c r="F95" s="74" t="s">
+      <c r="C95" s="54"/>
+      <c r="D95" s="50"/>
+      <c r="E95" s="51"/>
+      <c r="F95" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G95" s="75"/>
-      <c r="H95" s="76"/>
-      <c r="I95" s="52"/>
-      <c r="J95" s="49"/>
-    </row>
-    <row r="96" spans="2:10" ht="30" customHeight="1">
+      <c r="G95" s="77"/>
+      <c r="H95" s="78"/>
+      <c r="I95" s="54"/>
+      <c r="J95" s="51"/>
+    </row>
+    <row r="96" spans="2:10" ht="21" customHeight="1">
       <c r="B96" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="C96" s="52"/>
-      <c r="D96" s="48"/>
-      <c r="E96" s="49"/>
-      <c r="F96" s="74" t="s">
+      <c r="C96" s="54"/>
+      <c r="D96" s="50"/>
+      <c r="E96" s="51"/>
+      <c r="F96" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G96" s="75"/>
-      <c r="H96" s="76"/>
-      <c r="I96" s="52"/>
-      <c r="J96" s="49"/>
-    </row>
-    <row r="97" spans="2:10" ht="30" customHeight="1">
+      <c r="G96" s="77"/>
+      <c r="H96" s="78"/>
+      <c r="I96" s="54"/>
+      <c r="J96" s="51"/>
+    </row>
+    <row r="97" spans="2:10" ht="21" customHeight="1">
       <c r="B97" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="C97" s="52"/>
-      <c r="D97" s="48"/>
-      <c r="E97" s="49"/>
-      <c r="F97" s="74" t="s">
+      <c r="C97" s="54"/>
+      <c r="D97" s="50"/>
+      <c r="E97" s="51"/>
+      <c r="F97" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G97" s="75"/>
-      <c r="H97" s="76"/>
-      <c r="I97" s="52"/>
-      <c r="J97" s="49"/>
-    </row>
-    <row r="98" spans="2:10" ht="30" customHeight="1">
+      <c r="G97" s="77"/>
+      <c r="H97" s="78"/>
+      <c r="I97" s="54"/>
+      <c r="J97" s="51"/>
+    </row>
+    <row r="98" spans="2:10" ht="21" customHeight="1">
       <c r="B98" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="C98" s="52"/>
-      <c r="D98" s="48"/>
-      <c r="E98" s="49"/>
-      <c r="F98" s="74" t="s">
+      <c r="C98" s="54"/>
+      <c r="D98" s="50"/>
+      <c r="E98" s="51"/>
+      <c r="F98" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G98" s="75"/>
-      <c r="H98" s="76"/>
-      <c r="I98" s="52"/>
-      <c r="J98" s="49"/>
-    </row>
-    <row r="99" spans="2:10" ht="30" customHeight="1">
+      <c r="G98" s="77"/>
+      <c r="H98" s="78"/>
+      <c r="I98" s="54"/>
+      <c r="J98" s="51"/>
+    </row>
+    <row r="99" spans="2:10" ht="21" customHeight="1">
       <c r="B99" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="C99" s="52"/>
-      <c r="D99" s="48"/>
-      <c r="E99" s="49"/>
-      <c r="F99" s="74" t="s">
+      <c r="C99" s="54"/>
+      <c r="D99" s="50"/>
+      <c r="E99" s="51"/>
+      <c r="F99" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G99" s="75"/>
-      <c r="H99" s="76"/>
-      <c r="I99" s="52"/>
-      <c r="J99" s="49"/>
-    </row>
-    <row r="100" spans="2:10" ht="30" customHeight="1">
+      <c r="G99" s="77"/>
+      <c r="H99" s="78"/>
+      <c r="I99" s="54"/>
+      <c r="J99" s="51"/>
+    </row>
+    <row r="100" spans="2:10" ht="21" customHeight="1">
       <c r="B100" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="C100" s="48"/>
-      <c r="D100" s="48"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="48"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="48"/>
-      <c r="J100" s="49"/>
-    </row>
-    <row r="101" spans="2:10" ht="30" customHeight="1">
+      <c r="C100" s="50"/>
+      <c r="D100" s="50"/>
+      <c r="E100" s="50"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
+      <c r="H100" s="50"/>
+      <c r="I100" s="50"/>
+      <c r="J100" s="51"/>
+    </row>
+    <row r="101" spans="2:10" ht="21" customHeight="1">
       <c r="B101" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="C101" s="48"/>
-      <c r="D101" s="48"/>
-      <c r="E101" s="48"/>
-      <c r="F101" s="48"/>
-      <c r="G101" s="48"/>
-      <c r="H101" s="48"/>
-      <c r="I101" s="48"/>
-      <c r="J101" s="49"/>
-    </row>
-    <row r="102" spans="2:10" ht="30" customHeight="1">
-      <c r="B102" s="39" t="s">
+      <c r="C101" s="50"/>
+      <c r="D101" s="50"/>
+      <c r="E101" s="50"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
+      <c r="H101" s="50"/>
+      <c r="I101" s="50"/>
+      <c r="J101" s="51"/>
+    </row>
+    <row r="102" spans="2:10" ht="21" customHeight="1">
+      <c r="B102" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C102" s="40"/>
-      <c r="D102" s="40"/>
-      <c r="E102" s="40"/>
-      <c r="F102" s="40"/>
-      <c r="G102" s="40"/>
-      <c r="H102" s="40"/>
-      <c r="I102" s="40"/>
-      <c r="J102" s="41"/>
+      <c r="C102" s="42"/>
+      <c r="D102" s="42"/>
+      <c r="E102" s="42"/>
+      <c r="F102" s="42"/>
+      <c r="G102" s="42"/>
+      <c r="H102" s="42"/>
+      <c r="I102" s="42"/>
+      <c r="J102" s="43"/>
     </row>
     <row r="103" spans="2:10" ht="30" customHeight="1">
-      <c r="B103" s="99"/>
-      <c r="C103" s="100"/>
-      <c r="D103" s="100"/>
-      <c r="E103" s="100"/>
-      <c r="F103" s="100"/>
-      <c r="G103" s="100"/>
-      <c r="H103" s="100"/>
-      <c r="I103" s="100"/>
-      <c r="J103" s="101"/>
+      <c r="B103" s="103"/>
+      <c r="C103" s="104"/>
+      <c r="D103" s="104"/>
+      <c r="E103" s="104"/>
+      <c r="F103" s="104"/>
+      <c r="G103" s="104"/>
+      <c r="H103" s="104"/>
+      <c r="I103" s="104"/>
+      <c r="J103" s="105"/>
     </row>
     <row r="104" spans="2:10" ht="30" customHeight="1">
-      <c r="B104" s="102"/>
-      <c r="C104" s="103"/>
-      <c r="D104" s="103"/>
-      <c r="E104" s="103"/>
-      <c r="F104" s="103"/>
-      <c r="G104" s="103"/>
-      <c r="H104" s="103"/>
-      <c r="I104" s="103"/>
-      <c r="J104" s="104"/>
+      <c r="B104" s="106"/>
+      <c r="C104" s="107"/>
+      <c r="D104" s="107"/>
+      <c r="E104" s="107"/>
+      <c r="F104" s="107"/>
+      <c r="G104" s="107"/>
+      <c r="H104" s="107"/>
+      <c r="I104" s="107"/>
+      <c r="J104" s="108"/>
     </row>
     <row r="105" spans="2:10" ht="30" customHeight="1">
-      <c r="B105" s="105"/>
-      <c r="C105" s="106"/>
-      <c r="D105" s="106"/>
-      <c r="E105" s="106"/>
-      <c r="F105" s="106"/>
-      <c r="G105" s="106"/>
-      <c r="H105" s="106"/>
-      <c r="I105" s="106"/>
-      <c r="J105" s="107"/>
+      <c r="B105" s="109"/>
+      <c r="C105" s="110"/>
+      <c r="D105" s="110"/>
+      <c r="E105" s="110"/>
+      <c r="F105" s="110"/>
+      <c r="G105" s="110"/>
+      <c r="H105" s="110"/>
+      <c r="I105" s="110"/>
+      <c r="J105" s="111"/>
     </row>
     <row r="106" spans="2:10">
-      <c r="B106" s="84" t="s">
+      <c r="B106" s="88" t="s">
         <v>114</v>
       </c>
-      <c r="C106" s="85"/>
-      <c r="D106" s="86"/>
-      <c r="E106" s="93" t="s">
+      <c r="C106" s="89"/>
+      <c r="D106" s="90"/>
+      <c r="E106" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="F106" s="93"/>
-      <c r="G106" s="93"/>
-      <c r="H106" s="93"/>
-      <c r="I106" s="93"/>
-      <c r="J106" s="94"/>
+      <c r="F106" s="97"/>
+      <c r="G106" s="97"/>
+      <c r="H106" s="97"/>
+      <c r="I106" s="97"/>
+      <c r="J106" s="98"/>
     </row>
     <row r="107" spans="2:10">
-      <c r="B107" s="87"/>
-      <c r="C107" s="88"/>
-      <c r="D107" s="89"/>
-      <c r="E107" s="95"/>
-      <c r="F107" s="95"/>
-      <c r="G107" s="95"/>
-      <c r="H107" s="95"/>
-      <c r="I107" s="95"/>
-      <c r="J107" s="96"/>
+      <c r="B107" s="91"/>
+      <c r="C107" s="92"/>
+      <c r="D107" s="93"/>
+      <c r="E107" s="99"/>
+      <c r="F107" s="99"/>
+      <c r="G107" s="99"/>
+      <c r="H107" s="99"/>
+      <c r="I107" s="99"/>
+      <c r="J107" s="100"/>
     </row>
     <row r="108" spans="2:10" ht="71.400000000000006" customHeight="1">
-      <c r="B108" s="90"/>
-      <c r="C108" s="91"/>
-      <c r="D108" s="92"/>
-      <c r="E108" s="97"/>
-      <c r="F108" s="97"/>
-      <c r="G108" s="97"/>
-      <c r="H108" s="97"/>
-      <c r="I108" s="97"/>
-      <c r="J108" s="98"/>
+      <c r="B108" s="94"/>
+      <c r="C108" s="95"/>
+      <c r="D108" s="96"/>
+      <c r="E108" s="101"/>
+      <c r="F108" s="101"/>
+      <c r="G108" s="101"/>
+      <c r="H108" s="101"/>
+      <c r="I108" s="101"/>
+      <c r="J108" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="188">
@@ -3848,6 +3848,7 @@
     <mergeCell ref="I66:J66"/>
     <mergeCell ref="I74:J74"/>
     <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B74:C74"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
@@ -3938,7 +3939,6 @@
     <mergeCell ref="I61:J61"/>
     <mergeCell ref="I62:J62"/>
     <mergeCell ref="I63:J63"/>
-    <mergeCell ref="B74:C74"/>
     <mergeCell ref="C88:E88"/>
     <mergeCell ref="F88:H88"/>
     <mergeCell ref="I88:J88"/>

--- a/EquiposUnidos/app/src/main/res/raw/template_preven_excava.xlsx
+++ b/EquiposUnidos/app/src/main/res/raw/template_preven_excava.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Developer user\android\williApp\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elksi\Android\williApp\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EAF05E-E611-4BCD-B522-BDF435675E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B680E5F9-8D4C-4954-9040-36422A75CF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12504" tabRatio="840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FT-MANT-10" sheetId="14" r:id="rId1"/>
@@ -393,7 +393,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_-[$€-2]* #,##0.00_-;\-[$€-2]* #,##0.00_-;_-[$€-2]* &quot;-&quot;??_-"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,6 +580,11 @@
       <u/>
       <sz val="10"/>
       <color indexed="8"/>
+      <name val="Muller Regular"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Muller Regular"/>
     </font>
   </fonts>
@@ -1162,7 +1167,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -1487,35 +1492,44 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="60">
@@ -2358,16 +2372,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J108"/>
+  <dimension ref="B1:J110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="17" customWidth="1"/>
-    <col min="2" max="2" width="42.5546875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="54.5546875" style="17" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" style="17" customWidth="1"/>
-    <col min="6" max="7" width="14.44140625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="48.88671875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="52.6640625" style="17" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" style="17" customWidth="1"/>
+    <col min="5" max="5" width="9" style="17" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" style="17" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="17" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" style="17" customWidth="1"/>
     <col min="9" max="9" width="31.33203125" style="17" customWidth="1"/>
     <col min="10" max="10" width="29.44140625" style="17" customWidth="1"/>
     <col min="11" max="16384" width="11.44140625" style="17"/>
@@ -3379,8 +3394,8 @@
       <c r="F75" s="27"/>
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
-      <c r="I75" s="112"/>
-      <c r="J75" s="112"/>
+      <c r="I75" s="103"/>
+      <c r="J75" s="103"/>
     </row>
     <row r="76" spans="2:10" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B76" s="23" t="s">
@@ -3756,77 +3771,99 @@
       <c r="J102" s="43"/>
     </row>
     <row r="103" spans="2:10" ht="30" customHeight="1">
-      <c r="B103" s="103"/>
-      <c r="C103" s="104"/>
-      <c r="D103" s="104"/>
-      <c r="E103" s="104"/>
-      <c r="F103" s="104"/>
-      <c r="G103" s="104"/>
-      <c r="H103" s="104"/>
-      <c r="I103" s="104"/>
-      <c r="J103" s="105"/>
+      <c r="B103" s="107"/>
+      <c r="C103" s="108"/>
+      <c r="D103" s="108"/>
+      <c r="E103" s="108"/>
+      <c r="F103" s="108"/>
+      <c r="G103" s="108"/>
+      <c r="H103" s="108"/>
+      <c r="I103" s="108"/>
+      <c r="J103" s="109"/>
     </row>
     <row r="104" spans="2:10" ht="30" customHeight="1">
-      <c r="B104" s="106"/>
-      <c r="C104" s="107"/>
-      <c r="D104" s="107"/>
-      <c r="E104" s="107"/>
-      <c r="F104" s="107"/>
-      <c r="G104" s="107"/>
-      <c r="H104" s="107"/>
-      <c r="I104" s="107"/>
-      <c r="J104" s="108"/>
-    </row>
-    <row r="105" spans="2:10" ht="30" customHeight="1">
-      <c r="B105" s="109"/>
-      <c r="C105" s="110"/>
-      <c r="D105" s="110"/>
-      <c r="E105" s="110"/>
-      <c r="F105" s="110"/>
-      <c r="G105" s="110"/>
-      <c r="H105" s="110"/>
-      <c r="I105" s="110"/>
-      <c r="J105" s="111"/>
-    </row>
-    <row r="106" spans="2:10">
-      <c r="B106" s="88" t="s">
+      <c r="B104" s="110"/>
+      <c r="C104" s="111"/>
+      <c r="D104" s="111"/>
+      <c r="E104" s="111"/>
+      <c r="F104" s="111"/>
+      <c r="G104" s="111"/>
+      <c r="H104" s="111"/>
+      <c r="I104" s="111"/>
+      <c r="J104" s="112"/>
+    </row>
+    <row r="105" spans="2:10" ht="10.8" customHeight="1">
+      <c r="B105" s="113"/>
+      <c r="C105" s="114"/>
+      <c r="D105" s="114"/>
+      <c r="E105" s="114"/>
+      <c r="F105" s="114"/>
+      <c r="G105" s="114"/>
+      <c r="H105" s="114"/>
+      <c r="I105" s="114"/>
+      <c r="J105" s="115"/>
+    </row>
+    <row r="106" spans="2:10" ht="175.2" customHeight="1">
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="106"/>
+      <c r="E106" s="106"/>
+      <c r="F106" s="106"/>
+      <c r="G106" s="106"/>
+      <c r="H106" s="106"/>
+      <c r="I106" s="106"/>
+      <c r="J106" s="106"/>
+    </row>
+    <row r="107" spans="2:10" ht="30" customHeight="1">
+      <c r="B107" s="104"/>
+      <c r="C107" s="104"/>
+      <c r="D107" s="105"/>
+      <c r="E107" s="105"/>
+      <c r="F107" s="105"/>
+      <c r="G107" s="105"/>
+      <c r="H107" s="105"/>
+      <c r="I107" s="105"/>
+      <c r="J107" s="105"/>
+    </row>
+    <row r="108" spans="2:10">
+      <c r="B108" s="88" t="s">
         <v>114</v>
       </c>
-      <c r="C106" s="89"/>
-      <c r="D106" s="90"/>
-      <c r="E106" s="97" t="s">
+      <c r="C108" s="89"/>
+      <c r="D108" s="90"/>
+      <c r="E108" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="F106" s="97"/>
-      <c r="G106" s="97"/>
-      <c r="H106" s="97"/>
-      <c r="I106" s="97"/>
-      <c r="J106" s="98"/>
-    </row>
-    <row r="107" spans="2:10">
-      <c r="B107" s="91"/>
-      <c r="C107" s="92"/>
-      <c r="D107" s="93"/>
-      <c r="E107" s="99"/>
-      <c r="F107" s="99"/>
-      <c r="G107" s="99"/>
-      <c r="H107" s="99"/>
-      <c r="I107" s="99"/>
-      <c r="J107" s="100"/>
-    </row>
-    <row r="108" spans="2:10" ht="71.400000000000006" customHeight="1">
-      <c r="B108" s="94"/>
-      <c r="C108" s="95"/>
-      <c r="D108" s="96"/>
-      <c r="E108" s="101"/>
-      <c r="F108" s="101"/>
-      <c r="G108" s="101"/>
-      <c r="H108" s="101"/>
-      <c r="I108" s="101"/>
-      <c r="J108" s="102"/>
+      <c r="F108" s="97"/>
+      <c r="G108" s="97"/>
+      <c r="H108" s="97"/>
+      <c r="I108" s="97"/>
+      <c r="J108" s="98"/>
+    </row>
+    <row r="109" spans="2:10">
+      <c r="B109" s="91"/>
+      <c r="C109" s="92"/>
+      <c r="D109" s="93"/>
+      <c r="E109" s="99"/>
+      <c r="F109" s="99"/>
+      <c r="G109" s="99"/>
+      <c r="H109" s="99"/>
+      <c r="I109" s="99"/>
+      <c r="J109" s="100"/>
+    </row>
+    <row r="110" spans="2:10" ht="71.400000000000006" customHeight="1">
+      <c r="B110" s="94"/>
+      <c r="C110" s="95"/>
+      <c r="D110" s="96"/>
+      <c r="E110" s="101"/>
+      <c r="F110" s="101"/>
+      <c r="G110" s="101"/>
+      <c r="H110" s="101"/>
+      <c r="I110" s="101"/>
+      <c r="J110" s="102"/>
     </row>
   </sheetData>
-  <mergeCells count="188">
+  <mergeCells count="192">
     <mergeCell ref="I67:J67"/>
     <mergeCell ref="I68:J68"/>
     <mergeCell ref="I69:J69"/>
@@ -3858,8 +3895,8 @@
     <mergeCell ref="I44:J44"/>
     <mergeCell ref="I47:J47"/>
     <mergeCell ref="I39:J39"/>
-    <mergeCell ref="B106:D108"/>
-    <mergeCell ref="E106:J108"/>
+    <mergeCell ref="B108:D110"/>
+    <mergeCell ref="E108:J110"/>
     <mergeCell ref="C99:E99"/>
     <mergeCell ref="F99:H99"/>
     <mergeCell ref="I99:J99"/>
@@ -3867,6 +3904,10 @@
     <mergeCell ref="C101:J101"/>
     <mergeCell ref="B102:J102"/>
     <mergeCell ref="B103:J105"/>
+    <mergeCell ref="D106:H106"/>
+    <mergeCell ref="I106:J106"/>
+    <mergeCell ref="D107:H107"/>
+    <mergeCell ref="I107:J107"/>
     <mergeCell ref="C95:E95"/>
     <mergeCell ref="F95:H95"/>
     <mergeCell ref="I95:J95"/>
